--- a/fmcg_fnb_extract/FMCG_FnB_Dataset_FY2019-FY2024.xlsx
+++ b/fmcg_fnb_extract/FMCG_FnB_Dataset_FY2019-FY2024.xlsx
@@ -15202,7 +15202,7 @@
         <v>16.57</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="H2" t="n">
         <v>11.99</v>
